--- a/Databricks/ae outputs/hospital_model_performance_no.xlsx
+++ b/Databricks/ae outputs/hospital_model_performance_no.xlsx
@@ -408,19 +408,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>46.49433325440703</v>
+        <v>47.33444967734538</v>
       </c>
       <c r="C2">
-        <v>0.6821588981117277</v>
+        <v>0.6672776269821745</v>
       </c>
       <c r="D2">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
       <c r="F2">
-        <v>0.03838057342059029</v>
+        <v>0.03900333691277635</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -445,19 +445,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>34.01547793850995</v>
+        <v>33.36808096106073</v>
       </c>
       <c r="C3">
-        <v>0.6562063656861638</v>
+        <v>0.679490671503847</v>
       </c>
       <c r="D3">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E3">
         <v>500</v>
       </c>
       <c r="F3">
-        <v>0.05278150064810491</v>
+        <v>0.05151939377634129</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>30.34848576287424</v>
+        <v>29.81044832883516</v>
       </c>
       <c r="C4">
-        <v>0.5435389768111231</v>
+        <v>0.5614955846429556</v>
       </c>
       <c r="D4">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E4">
         <v>500</v>
       </c>
       <c r="F4">
-        <v>0.04818563620170133</v>
+        <v>0.0472671534357125</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>16.26092344233312</v>
+        <v>15.4716130259001</v>
       </c>
       <c r="C5">
-        <v>0.5119458329799657</v>
+        <v>0.5651606017038335</v>
       </c>
       <c r="D5">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
       <c r="F5">
-        <v>0.09233489370262819</v>
+        <v>0.0876016138413489</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>30.19176859166994</v>
+        <v>29.62476113555033</v>
       </c>
       <c r="C6">
-        <v>0.320100996694096</v>
+        <v>0.3440306549029083</v>
       </c>
       <c r="D6">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E6">
         <v>500</v>
       </c>
       <c r="F6">
-        <v>0.05387227227487404</v>
+        <v>0.05281082632549616</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>36.94602427452214</v>
+        <v>36.12166182611958</v>
       </c>
       <c r="C7">
-        <v>0.6262827666645755</v>
+        <v>0.6507203639607806</v>
       </c>
       <c r="D7">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E7">
         <v>500</v>
       </c>
       <c r="F7">
-        <v>0.03427790617245033</v>
+        <v>0.03347532574181034</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>39.77712353590125</v>
+        <v>40.73849504622791</v>
       </c>
       <c r="C8">
-        <v>0.7499037485586925</v>
+        <v>0.7398721632190564</v>
       </c>
       <c r="D8">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E8">
         <v>500</v>
       </c>
       <c r="F8">
-        <v>0.02987725478742075</v>
+        <v>0.03056885002118131</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>65.78741069155895</v>
+        <v>62.89331220137833</v>
       </c>
       <c r="C9">
-        <v>0.4959773477435798</v>
+        <v>0.5429612468318159</v>
       </c>
       <c r="D9">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E9">
         <v>500</v>
       </c>
       <c r="F9">
-        <v>0.04093906059938075</v>
+        <v>0.039108864914796</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>64.99804999798062</v>
+        <v>61.27065291812412</v>
       </c>
       <c r="C10">
-        <v>0.5201814343748333</v>
+        <v>0.5646763421104505</v>
       </c>
       <c r="D10">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E10">
         <v>500</v>
       </c>
       <c r="F10">
-        <v>0.03357009240672375</v>
+        <v>0.03163107262530672</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>97.63220439597237</v>
+        <v>96.67354876408619</v>
       </c>
       <c r="C11">
-        <v>0.6830135580954528</v>
+        <v>0.6850267506929911</v>
       </c>
       <c r="D11">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E11">
         <v>500</v>
       </c>
       <c r="F11">
-        <v>0.06756996273301305</v>
+        <v>0.06688421236583948</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>15.68875753180156</v>
+        <v>15.19741920199011</v>
       </c>
       <c r="C12">
-        <v>0.4655327756397026</v>
+        <v>0.4993130040444646</v>
       </c>
       <c r="D12">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E12">
         <v>500</v>
       </c>
       <c r="F12">
-        <v>0.08466185789785717</v>
+        <v>0.08185912382571518</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>30.99356563201531</v>
+        <v>29.54034283892766</v>
       </c>
       <c r="C13">
-        <v>0.7348719147065071</v>
+        <v>0.7639232670349994</v>
       </c>
       <c r="D13">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E13">
         <v>500</v>
       </c>
       <c r="F13">
-        <v>0.04057108235780604</v>
+        <v>0.03858859708293403</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -852,19 +852,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>16.30791036801128</v>
+        <v>16.37918030295105</v>
       </c>
       <c r="C14">
-        <v>0.7763808732130766</v>
+        <v>0.7773071115067921</v>
       </c>
       <c r="D14">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E14">
         <v>500</v>
       </c>
       <c r="F14">
-        <v>0.09083135384862522</v>
+        <v>0.09118456967943356</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>41.91726927992283</v>
+        <v>42.07427136178352</v>
       </c>
       <c r="C15">
-        <v>0.6533371829860668</v>
+        <v>0.6546368988449008</v>
       </c>
       <c r="D15">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E15">
         <v>500</v>
       </c>
       <c r="F15">
-        <v>0.03380130248795102</v>
+        <v>0.03389369027661881</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>46.04622434982161</v>
+        <v>45.42742015145911</v>
       </c>
       <c r="C16">
-        <v>0.648104905569906</v>
+        <v>0.6600102013042477</v>
       </c>
       <c r="D16">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E16">
         <v>500</v>
       </c>
       <c r="F16">
-        <v>0.03766021134294303</v>
+        <v>0.03711835308543979</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>45.50079377860992</v>
+        <v>47.16502053009039</v>
       </c>
       <c r="C17">
-        <v>0.6342262646132728</v>
+        <v>0.6060589725996552</v>
       </c>
       <c r="D17">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E17">
         <v>500</v>
       </c>
       <c r="F17">
-        <v>0.03377935692547136</v>
+        <v>0.03501694275093576</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>35.4351804396951</v>
+        <v>34.38971075172815</v>
       </c>
       <c r="C18">
-        <v>0.7455295299677986</v>
+        <v>0.7678403762408899</v>
       </c>
       <c r="D18">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>0.03247913980971619</v>
+        <v>0.03146897068580924</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>33.71704586418945</v>
+        <v>33.24096000359237</v>
       </c>
       <c r="C19">
-        <v>0.6471452666401072</v>
+        <v>0.6552858799173152</v>
       </c>
       <c r="D19">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E19">
         <v>500</v>
       </c>
       <c r="F19">
-        <v>0.09601929551472078</v>
+        <v>0.09452405688225318</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>29.6418154030207</v>
+        <v>28.89823477980951</v>
       </c>
       <c r="C20">
-        <v>0.6491038354465648</v>
+        <v>0.6698833331316586</v>
       </c>
       <c r="D20">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E20">
         <v>500</v>
       </c>
       <c r="F20">
-        <v>0.05851815013935365</v>
+        <v>0.0569281258795365</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>15.05990891862479</v>
+        <v>15.04169686778516</v>
       </c>
       <c r="C21">
-        <v>0.4852173598998777</v>
+        <v>0.4808613605539068</v>
       </c>
       <c r="D21">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E21">
         <v>500</v>
       </c>
       <c r="F21">
-        <v>0.1023072854106522</v>
+        <v>0.1022688119920122</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>36.95858047908116</v>
+        <v>36.70063169978699</v>
       </c>
       <c r="C22">
-        <v>0.7243823446853056</v>
+        <v>0.7293839212687151</v>
       </c>
       <c r="D22">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E22">
         <v>500</v>
       </c>
       <c r="F22">
-        <v>0.03357849642662288</v>
+        <v>0.03331171944189791</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>75.94759892022134</v>
+        <v>72.61216887255566</v>
       </c>
       <c r="C23">
-        <v>0.6398567244992773</v>
+        <v>0.667427589094516</v>
       </c>
       <c r="D23">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E23">
         <v>500</v>
       </c>
       <c r="F23">
-        <v>0.03161617182675828</v>
+        <v>0.03020389154733188</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>77.25347467497163</v>
+        <v>76.02165513980692</v>
       </c>
       <c r="C24">
-        <v>0.6815135103524624</v>
+        <v>0.6883630078860576</v>
       </c>
       <c r="D24">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E24">
         <v>500</v>
       </c>
       <c r="F24">
-        <v>0.07512361857010567</v>
+        <v>0.0738351502244923</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>42.03585644409962</v>
+        <v>43.2290977080113</v>
       </c>
       <c r="C25">
-        <v>0.6767425214247695</v>
+        <v>0.6576050756013647</v>
       </c>
       <c r="D25">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E25">
         <v>500</v>
       </c>
       <c r="F25">
-        <v>0.03541473645885321</v>
+        <v>0.03642492223458991</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>27.31490451493142</v>
+        <v>27.18072268958199</v>
       </c>
       <c r="C26">
-        <v>0.577309610159242</v>
+        <v>0.5988593167962911</v>
       </c>
       <c r="D26">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E26">
         <v>500</v>
       </c>
       <c r="F26">
-        <v>0.06069614239700094</v>
+        <v>0.06023562337022868</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1333,19 +1333,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>37.95973600363648</v>
+        <v>37.94326857966445</v>
       </c>
       <c r="C27">
-        <v>0.6902709772423981</v>
+        <v>0.6994109696266482</v>
       </c>
       <c r="D27">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E27">
         <v>500</v>
       </c>
       <c r="F27">
-        <v>0.0323668344829191</v>
+        <v>0.03231231002015254</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>11.61618883957597</v>
+        <v>12.01180366550235</v>
       </c>
       <c r="C28">
-        <v>0.5045168944900501</v>
+        <v>0.4750120832076388</v>
       </c>
       <c r="D28">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E28">
         <v>500</v>
       </c>
       <c r="F28">
-        <v>0.1043581369586769</v>
+        <v>0.1072482470134139</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>18.98196180970888</v>
+        <v>18.75408621171955</v>
       </c>
       <c r="C29">
-        <v>0.4225009942085635</v>
+        <v>0.4337844465027483</v>
       </c>
       <c r="D29">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E29">
         <v>500</v>
       </c>
       <c r="F29">
-        <v>0.07173246726169222</v>
+        <v>0.07093073453751719</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>32.46914639837345</v>
+        <v>33.62187903310593</v>
       </c>
       <c r="C30">
-        <v>0.7831244168701935</v>
+        <v>0.7664756884548682</v>
       </c>
       <c r="D30">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E30">
         <v>500</v>
       </c>
       <c r="F30">
-        <v>0.0465147000964018</v>
+        <v>0.04813302272391046</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>14.26283739718588</v>
+        <v>14.26811537470815</v>
       </c>
       <c r="C31">
-        <v>0.4494042352585648</v>
+        <v>0.4506417652388295</v>
       </c>
       <c r="D31">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E31">
         <v>500</v>
       </c>
       <c r="F31">
-        <v>0.08841836034110373</v>
+        <v>0.08838029840626953</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>37.43070039517617</v>
+        <v>37.36026665411789</v>
       </c>
       <c r="C32">
-        <v>0.7981094187109143</v>
+        <v>0.7945171240841046</v>
       </c>
       <c r="D32">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E32">
         <v>1000</v>
       </c>
       <c r="F32">
-        <v>0.03089864170844962</v>
+        <v>0.03078466270115185</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1555,19 +1555,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>34.12972028631665</v>
+        <v>33.24774485882744</v>
       </c>
       <c r="C33">
-        <v>0.6513166645527161</v>
+        <v>0.6816388959535662</v>
       </c>
       <c r="D33">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E33">
         <v>1000</v>
       </c>
       <c r="F33">
-        <v>0.05295876943632247</v>
+        <v>0.05133359816395047</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>29.235319694997</v>
+        <v>28.40748067282648</v>
       </c>
       <c r="C34">
-        <v>0.5700473861276555</v>
+        <v>0.5977429275982022</v>
       </c>
       <c r="D34">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E34">
         <v>1000</v>
       </c>
       <c r="F34">
-        <v>0.04641821308880163</v>
+        <v>0.04504262173023797</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1629,19 +1629,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>15.42433743161232</v>
+        <v>15.28015147981607</v>
       </c>
       <c r="C35">
-        <v>0.5403287344913315</v>
+        <v>0.562163226730574</v>
       </c>
       <c r="D35">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E35">
         <v>1000</v>
       </c>
       <c r="F35">
-        <v>0.087584482039542</v>
+        <v>0.08651754197389443</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>29.60163663819558</v>
+        <v>28.75778297056763</v>
       </c>
       <c r="C36">
-        <v>0.3394534400179265</v>
+        <v>0.3696485682173424</v>
       </c>
       <c r="D36">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E36">
         <v>1000</v>
       </c>
       <c r="F36">
-        <v>0.0528192783378297</v>
+        <v>0.05126530050372153</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1703,19 +1703,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>31.81916908306097</v>
+        <v>31.06412186326894</v>
       </c>
       <c r="C37">
-        <v>0.7230866892034168</v>
+        <v>0.7402109019268284</v>
       </c>
       <c r="D37">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E37">
         <v>1000</v>
       </c>
       <c r="F37">
-        <v>0.02952129528769448</v>
+        <v>0.02878830999697476</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>33.61603636177525</v>
+        <v>33.17403914470034</v>
       </c>
       <c r="C38">
-        <v>0.8232276470009428</v>
+        <v>0.8279789493046129</v>
       </c>
       <c r="D38">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E38">
         <v>1000</v>
       </c>
       <c r="F38">
-        <v>0.02524956040165823</v>
+        <v>0.02489272679465464</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1777,19 +1777,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>59.64446820945306</v>
+        <v>55.97036499682015</v>
       </c>
       <c r="C39">
-        <v>0.576210432833965</v>
+        <v>0.6217904594226294</v>
       </c>
       <c r="D39">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E39">
         <v>1000</v>
       </c>
       <c r="F39">
-        <v>0.03711634905183978</v>
+        <v>0.03480397783604874</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>58.393204060884</v>
+        <v>55.47242533761947</v>
       </c>
       <c r="C40">
-        <v>0.6030583708808438</v>
+        <v>0.6403811492684789</v>
       </c>
       <c r="D40">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E40">
         <v>1000</v>
       </c>
       <c r="F40">
-        <v>0.03015883178509901</v>
+        <v>0.02863772835750396</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>81.39944543352939</v>
+        <v>78.6856831171315</v>
       </c>
       <c r="C41">
-        <v>0.780635543536271</v>
+        <v>0.7930081530764144</v>
       </c>
       <c r="D41">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E41">
         <v>1000</v>
       </c>
       <c r="F41">
-        <v>0.05633548405938082</v>
+        <v>0.05443919259238462</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>15.10085337697159</v>
+        <v>14.86689801863824</v>
       </c>
       <c r="C42">
-        <v>0.4822744933172856</v>
+        <v>0.5016587864206827</v>
       </c>
       <c r="D42">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E42">
         <v>1000</v>
       </c>
       <c r="F42">
-        <v>0.08148932763770857</v>
+        <v>0.08007881006879258</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1925,19 +1925,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>30.77270973038397</v>
+        <v>29.09599956993332</v>
       </c>
       <c r="C43">
-        <v>0.7371224447373209</v>
+        <v>0.7747990633457051</v>
       </c>
       <c r="D43">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E43">
         <v>1000</v>
       </c>
       <c r="F43">
-        <v>0.04028197838439819</v>
+        <v>0.03800815076018043</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1962,19 +1962,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>16.18067092337338</v>
+        <v>16.1675015699355</v>
       </c>
       <c r="C44">
-        <v>0.7752397310701824</v>
+        <v>0.7759117356790403</v>
       </c>
       <c r="D44">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E44">
         <v>1000</v>
       </c>
       <c r="F44">
-        <v>0.09012265906440088</v>
+        <v>0.09000613255234284</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1999,19 +1999,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>34.32261359275291</v>
+        <v>33.24041073351636</v>
       </c>
       <c r="C45">
-        <v>0.7646077043633425</v>
+        <v>0.7796814351522104</v>
       </c>
       <c r="D45">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E45">
         <v>1000</v>
       </c>
       <c r="F45">
-        <v>0.02767711409057313</v>
+        <v>0.02677741407288487</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2036,19 +2036,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>37.36359466476471</v>
+        <v>37.99240279866277</v>
       </c>
       <c r="C46">
-        <v>0.7661582252179419</v>
+        <v>0.7576933470201691</v>
       </c>
       <c r="D46">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E46">
         <v>1000</v>
       </c>
       <c r="F46">
-        <v>0.03055887624828786</v>
+        <v>0.03104326455130471</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>37.61433147869957</v>
+        <v>38.48174761187668</v>
       </c>
       <c r="C47">
-        <v>0.7528224930055586</v>
+        <v>0.7384221538621053</v>
       </c>
       <c r="D47">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E47">
         <v>1000</v>
       </c>
       <c r="F47">
-        <v>0.02792452225590169</v>
+        <v>0.02857018056891032</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2110,19 +2110,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>30.07142673086196</v>
+        <v>28.87920670669642</v>
       </c>
       <c r="C48">
-        <v>0.820668944974017</v>
+        <v>0.8398611975120281</v>
       </c>
       <c r="D48">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E48">
         <v>1000</v>
       </c>
       <c r="F48">
-        <v>0.02756283616874695</v>
+        <v>0.02642647726360381</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2147,19 +2147,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>33.27196367040963</v>
+        <v>32.83006873509197</v>
       </c>
       <c r="C49">
-        <v>0.6503539029728914</v>
+        <v>0.6591726766249834</v>
       </c>
       <c r="D49">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E49">
         <v>1000</v>
       </c>
       <c r="F49">
-        <v>0.09475179186493411</v>
+        <v>0.09335564569220466</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>29.40605557924493</v>
+        <v>28.82329454741541</v>
       </c>
       <c r="C50">
-        <v>0.6497208035636731</v>
+        <v>0.6706402362474833</v>
       </c>
       <c r="D50">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E50">
         <v>1000</v>
       </c>
       <c r="F50">
-        <v>0.05805271883641355</v>
+        <v>0.05678049724354265</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>14.80995975038469</v>
+        <v>14.71998357931726</v>
       </c>
       <c r="C51">
-        <v>0.4789090452765793</v>
+        <v>0.4768331862803298</v>
       </c>
       <c r="D51">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E51">
         <v>1000</v>
       </c>
       <c r="F51">
-        <v>0.1006092923463203</v>
+        <v>0.100081476606726</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>31.7055712171958</v>
+        <v>31.24648679844136</v>
       </c>
       <c r="C52">
-        <v>0.7965643473375706</v>
+        <v>0.8030303362122096</v>
       </c>
       <c r="D52">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E52">
         <v>1000</v>
       </c>
       <c r="F52">
-        <v>0.02880590639630308</v>
+        <v>0.028361206703172</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2295,19 +2295,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>74.74932298385046</v>
+        <v>74.54607818907402</v>
       </c>
       <c r="C53">
-        <v>0.6450105678305423</v>
+        <v>0.655222438246691</v>
       </c>
       <c r="D53">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E53">
         <v>1000</v>
       </c>
       <c r="F53">
-        <v>0.03111734239121592</v>
+        <v>0.03100832402973047</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2332,19 +2332,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>63.96362866414099</v>
+        <v>62.97197576371122</v>
       </c>
       <c r="C54">
-        <v>0.7802554443685467</v>
+        <v>0.7846113348779566</v>
       </c>
       <c r="D54">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E54">
         <v>1000</v>
       </c>
       <c r="F54">
-        <v>0.062200169796137</v>
+        <v>0.06116080058893749</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>33.57250390644953</v>
+        <v>33.88136620293444</v>
       </c>
       <c r="C55">
-        <v>0.7930504854508468</v>
+        <v>0.7860024456081685</v>
       </c>
       <c r="D55">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E55">
         <v>1000</v>
       </c>
       <c r="F55">
-        <v>0.02828445709657045</v>
+        <v>0.02854850539512507</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2406,19 +2406,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>26.98490438514023</v>
+        <v>26.42101128497934</v>
       </c>
       <c r="C56">
-        <v>0.5932852921038002</v>
+        <v>0.611713993087712</v>
       </c>
       <c r="D56">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E56">
         <v>1000</v>
       </c>
       <c r="F56">
-        <v>0.05996285281665897</v>
+        <v>0.05855201508062082</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2443,19 +2443,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>30.71888335182818</v>
+        <v>30.2756143902812</v>
       </c>
       <c r="C57">
-        <v>0.796400778676345</v>
+        <v>0.8059547625390607</v>
       </c>
       <c r="D57">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E57">
         <v>1000</v>
       </c>
       <c r="F57">
-        <v>0.02619283265967582</v>
+        <v>0.02578257158250358</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2480,19 +2480,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>11.48916437067259</v>
+        <v>10.98608419431637</v>
       </c>
       <c r="C58">
-        <v>0.4579044213860243</v>
+        <v>0.5158159498523996</v>
       </c>
       <c r="D58">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E58">
         <v>1000</v>
       </c>
       <c r="F58">
-        <v>0.1032169677588651</v>
+        <v>0.09809003744925331</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>18.25119104466176</v>
+        <v>18.27456467231426</v>
       </c>
       <c r="C59">
-        <v>0.4518890759442061</v>
+        <v>0.4441227812078409</v>
       </c>
       <c r="D59">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E59">
         <v>1000</v>
       </c>
       <c r="F59">
-        <v>0.0689708986469702</v>
+        <v>0.06911711298152143</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2554,19 +2554,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>32.54464973220322</v>
+        <v>32.68349742694589</v>
       </c>
       <c r="C60">
-        <v>0.7816992618022339</v>
+        <v>0.7792954297741514</v>
       </c>
       <c r="D60">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E60">
         <v>1000</v>
       </c>
       <c r="F60">
-        <v>0.04662286477946062</v>
+        <v>0.04678963727158262</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>14.35533520828302</v>
+        <v>14.28921774648627</v>
       </c>
       <c r="C61">
-        <v>0.4201487205631637</v>
+        <v>0.4223560569879213</v>
       </c>
       <c r="D61">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E61">
         <v>1000</v>
       </c>
       <c r="F61">
-        <v>0.08899177393088244</v>
+        <v>0.08851101180925589</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2628,19 +2628,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>30.98257107242751</v>
+        <v>31.02768082335846</v>
       </c>
       <c r="C62">
-        <v>0.8694321853423094</v>
+        <v>0.8638774927981746</v>
       </c>
       <c r="D62">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E62">
         <v>2000</v>
       </c>
       <c r="F62">
-        <v>0.02557578011275703</v>
+        <v>0.02556664537191699</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2665,19 +2665,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>32.54172330642157</v>
+        <v>32.04571602308265</v>
       </c>
       <c r="C63">
-        <v>0.6796035355536136</v>
+        <v>0.7025416758487786</v>
       </c>
       <c r="D63">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E63">
         <v>2000</v>
       </c>
       <c r="F63">
-        <v>0.05049468929683311</v>
+        <v>0.04947769889927534</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2702,19 +2702,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>27.82743915774003</v>
+        <v>27.52473009945425</v>
       </c>
       <c r="C64">
-        <v>0.6071368363551288</v>
+        <v>0.6212134704309654</v>
       </c>
       <c r="D64">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E64">
         <v>2000</v>
       </c>
       <c r="F64">
-        <v>0.04418285874810141</v>
+        <v>0.04364294111031624</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2739,19 +2739,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>15.41097957806962</v>
+        <v>15.93293253529697</v>
       </c>
       <c r="C65">
-        <v>0.5420748702015589</v>
+        <v>0.5250373862926018</v>
       </c>
       <c r="D65">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E65">
         <v>2000</v>
       </c>
       <c r="F65">
-        <v>0.08750863173550889</v>
+        <v>0.09021364488504247</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2776,19 +2776,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>28.13555201545193</v>
+        <v>28.81288276476063</v>
       </c>
       <c r="C66">
-        <v>0.3843849010691283</v>
+        <v>0.3634038978503634</v>
       </c>
       <c r="D66">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E66">
         <v>2000</v>
       </c>
       <c r="F66">
-        <v>0.05020329015102823</v>
+        <v>0.05136352460917112</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2813,19 +2813,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>26.49464822835969</v>
+        <v>26.82580580226002</v>
       </c>
       <c r="C67">
-        <v>0.812609325486674</v>
+        <v>0.8103560715342389</v>
       </c>
       <c r="D67">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E67">
         <v>2000</v>
       </c>
       <c r="F67">
-        <v>0.02458129349170783</v>
+        <v>0.02486050037896801</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2850,19 +2850,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>27.51036315680549</v>
+        <v>27.35423932122627</v>
       </c>
       <c r="C68">
-        <v>0.883112081580299</v>
+        <v>0.8845772658898889</v>
       </c>
       <c r="D68">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E68">
         <v>2000</v>
       </c>
       <c r="F68">
-        <v>0.02066348836382061</v>
+        <v>0.02052573710209973</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>52.74179640798228</v>
+        <v>51.14434403917851</v>
       </c>
       <c r="C69">
-        <v>0.6613793879243559</v>
+        <v>0.6802242726596105</v>
       </c>
       <c r="D69">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E69">
         <v>2000</v>
       </c>
       <c r="F69">
-        <v>0.03282086308868258</v>
+        <v>0.03180301962440212</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2924,19 +2924,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>53.82206564591981</v>
+        <v>52.56958853605356</v>
       </c>
       <c r="C70">
-        <v>0.6630486716166363</v>
+        <v>0.6743761204056302</v>
       </c>
       <c r="D70">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E70">
         <v>2000</v>
       </c>
       <c r="F70">
-        <v>0.02779793728135559</v>
+        <v>0.02713913421305371</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2961,19 +2961,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>65.44711201333412</v>
+        <v>65.45886577418543</v>
       </c>
       <c r="C71">
-        <v>0.8595172052506872</v>
+        <v>0.856571695673325</v>
       </c>
       <c r="D71">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E71">
         <v>2000</v>
       </c>
       <c r="F71">
-        <v>0.04529508421000837</v>
+        <v>0.04528813450669631</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2998,19 +2998,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>15.15617293645336</v>
+        <v>14.9834507663783</v>
       </c>
       <c r="C72">
-        <v>0.4757818434437468</v>
+        <v>0.4908156321846178</v>
       </c>
       <c r="D72">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E72">
         <v>2000</v>
       </c>
       <c r="F72">
-        <v>0.08178785074728713</v>
+        <v>0.0807066078338389</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3035,19 +3035,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>28.68408960148722</v>
+        <v>29.48040169440741</v>
       </c>
       <c r="C73">
-        <v>0.7712516791634009</v>
+        <v>0.7699911384479723</v>
       </c>
       <c r="D73">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E73">
         <v>2000</v>
       </c>
       <c r="F73">
-        <v>0.03754794060798596</v>
+        <v>0.03851029587000655</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>15.69313616223397</v>
+        <v>16.53912387203511</v>
       </c>
       <c r="C74">
-        <v>0.7896730680315381</v>
+        <v>0.7652055308697762</v>
       </c>
       <c r="D74">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E74">
         <v>2000</v>
       </c>
       <c r="F74">
-        <v>0.08740720126488889</v>
+        <v>0.09207499186480356</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>27.75822692020073</v>
+        <v>27.33587884922646</v>
       </c>
       <c r="C75">
-        <v>0.8478280398064393</v>
+        <v>0.8530548987253981</v>
       </c>
       <c r="D75">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E75">
         <v>2000</v>
       </c>
       <c r="F75">
-        <v>0.0223837153702255</v>
+        <v>0.02202091162050208</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3146,19 +3146,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>32.17273994992841</v>
+        <v>31.15009081556138</v>
       </c>
       <c r="C76">
-        <v>0.8280217907046893</v>
+        <v>0.8402191846446291</v>
       </c>
       <c r="D76">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E76">
         <v>2000</v>
       </c>
       <c r="F76">
-        <v>0.02631338840706804</v>
+        <v>0.02545247046124376</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>31.23895231751002</v>
+        <v>31.62096085590337</v>
       </c>
       <c r="C77">
-        <v>0.8359510721752518</v>
+        <v>0.8273697880199417</v>
       </c>
       <c r="D77">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E77">
         <v>2000</v>
       </c>
       <c r="F77">
-        <v>0.02319150134930217</v>
+        <v>0.02347649515628498</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3220,19 +3220,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>26.32051891142917</v>
+        <v>25.2779598290059</v>
       </c>
       <c r="C78">
-        <v>0.8659860576276368</v>
+        <v>0.8819343990217343</v>
       </c>
       <c r="D78">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E78">
         <v>2000</v>
       </c>
       <c r="F78">
-        <v>0.02412483308906619</v>
+        <v>0.02313108657990316</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3257,19 +3257,19 @@
         </is>
       </c>
       <c r="B79">
-        <v>33.9344599115403</v>
+        <v>33.28748724463151</v>
       </c>
       <c r="C79">
-        <v>0.6403329357882862</v>
+        <v>0.6534427753594028</v>
       </c>
       <c r="D79">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E79">
         <v>2000</v>
       </c>
       <c r="F79">
-        <v>0.09663844654431335</v>
+        <v>0.09465636183307537</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3294,19 +3294,19 @@
         </is>
       </c>
       <c r="B80">
-        <v>29.03845077929634</v>
+        <v>29.14490923349251</v>
       </c>
       <c r="C80">
-        <v>0.6587942991091279</v>
+        <v>0.6622732788636549</v>
       </c>
       <c r="D80">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E80">
         <v>2000</v>
       </c>
       <c r="F80">
-        <v>0.05732700239216544</v>
+        <v>0.05741406263164367</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3331,19 +3331,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>14.21756839533312</v>
+        <v>14.57572478624041</v>
       </c>
       <c r="C81">
-        <v>0.5114202278152459</v>
+        <v>0.4808670563899965</v>
       </c>
       <c r="D81">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E81">
         <v>2000</v>
       </c>
       <c r="F81">
-        <v>0.09658496844346379</v>
+        <v>0.09910065805167535</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3368,19 +3368,19 @@
         </is>
       </c>
       <c r="B82">
-        <v>26.97254799227818</v>
+        <v>26.47905808143308</v>
       </c>
       <c r="C82">
-        <v>0.8540515915727648</v>
+        <v>0.8605536257084488</v>
       </c>
       <c r="D82">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E82">
         <v>2000</v>
       </c>
       <c r="F82">
-        <v>0.02450574655831975</v>
+        <v>0.02403399922676365</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3405,19 +3405,19 @@
         </is>
       </c>
       <c r="B83">
-        <v>79.54137315715558</v>
+        <v>79.27507531627556</v>
       </c>
       <c r="C83">
-        <v>0.6171742943923701</v>
+        <v>0.6171920435457765</v>
       </c>
       <c r="D83">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E83">
         <v>2000</v>
       </c>
       <c r="F83">
-        <v>0.03311222154257409</v>
+        <v>0.03297540638762467</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3442,19 +3442,19 @@
         </is>
       </c>
       <c r="B84">
-        <v>52.80584853628979</v>
+        <v>53.89049519919529</v>
       </c>
       <c r="C84">
-        <v>0.8488234063735719</v>
+        <v>0.8416767783069411</v>
       </c>
       <c r="D84">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E84">
         <v>2000</v>
       </c>
       <c r="F84">
-        <v>0.05135000646121377</v>
+        <v>0.05234051799302841</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3479,19 +3479,19 @@
         </is>
       </c>
       <c r="B85">
-        <v>27.47682887489076</v>
+        <v>28.64574498273345</v>
       </c>
       <c r="C85">
-        <v>0.8661065784516144</v>
+        <v>0.8510756308150755</v>
       </c>
       <c r="D85">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E85">
         <v>2000</v>
       </c>
       <c r="F85">
-        <v>0.02314891941415058</v>
+        <v>0.02413696072020008</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3516,19 +3516,19 @@
         </is>
       </c>
       <c r="B86">
-        <v>26.79611178772305</v>
+        <v>26.66385710565421</v>
       </c>
       <c r="C86">
-        <v>0.5877627242370268</v>
+        <v>0.6047554338612785</v>
       </c>
       <c r="D86">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E86">
         <v>2000</v>
       </c>
       <c r="F86">
-        <v>0.05954333890731804</v>
+        <v>0.05909018949041354</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3553,19 +3553,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>24.50698692530622</v>
+        <v>25.02546049937985</v>
       </c>
       <c r="C87">
-        <v>0.8714195759499956</v>
+        <v>0.868165102257914</v>
       </c>
       <c r="D87">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E87">
         <v>2000</v>
       </c>
       <c r="F87">
-        <v>0.02089618298215931</v>
+        <v>0.02131156508974099</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3590,19 +3590,19 @@
         </is>
       </c>
       <c r="B88">
-        <v>11.12481367108188</v>
+        <v>11.4545919051122</v>
       </c>
       <c r="C88">
-        <v>0.4775698796586616</v>
+        <v>0.4605988035841166</v>
       </c>
       <c r="D88">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E88">
         <v>2000</v>
       </c>
       <c r="F88">
-        <v>0.09994369450771631</v>
+        <v>0.1022731420099304</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3627,19 +3627,19 @@
         </is>
       </c>
       <c r="B89">
-        <v>19.00401814455854</v>
+        <v>18.55954533632122</v>
       </c>
       <c r="C89">
-        <v>0.4142442373724089</v>
+        <v>0.4350806052925013</v>
       </c>
       <c r="D89">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E89">
         <v>2000</v>
       </c>
       <c r="F89">
-        <v>0.07181581772532593</v>
+        <v>0.07019495210408934</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
         </is>
       </c>
       <c r="B90">
-        <v>31.45441324706886</v>
+        <v>31.89296717235108</v>
       </c>
       <c r="C90">
-        <v>0.796135816567096</v>
+        <v>0.7883713415430175</v>
       </c>
       <c r="D90">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E90">
         <v>2000</v>
       </c>
       <c r="F90">
-        <v>0.04506101210498686</v>
+        <v>0.04565791555338584</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="B91">
-        <v>14.50533847413503</v>
+        <v>14.60634884189106</v>
       </c>
       <c r="C91">
-        <v>0.413973484942176</v>
+        <v>0.3935164397733367</v>
       </c>
       <c r="D91">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E91">
         <v>2000</v>
       </c>
       <c r="F91">
-        <v>0.08992167605646244</v>
+        <v>0.09047540164699616</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3738,19 +3738,19 @@
         </is>
       </c>
       <c r="B92">
-        <v>23.48295127982832</v>
+        <v>22.34639233774439</v>
       </c>
       <c r="C92">
-        <v>0.9326336662080039</v>
+        <v>0.9366356601175243</v>
       </c>
       <c r="D92">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E92">
         <v>5000</v>
       </c>
       <c r="F92">
-        <v>0.01938492441209845</v>
+        <v>0.01841330944112095</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3775,19 +3775,19 @@
         </is>
       </c>
       <c r="B93">
-        <v>24.53976949122141</v>
+        <v>25.407371753418</v>
       </c>
       <c r="C93">
-        <v>0.8191879345004115</v>
+        <v>0.8131998824136932</v>
       </c>
       <c r="D93">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E93">
         <v>5000</v>
       </c>
       <c r="F93">
-        <v>0.03807813200939509</v>
+        <v>0.03922827901651742</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3812,19 +3812,19 @@
         </is>
       </c>
       <c r="B94">
-        <v>22.01097911875425</v>
+        <v>21.92885003105519</v>
       </c>
       <c r="C94">
-        <v>0.7581674181688415</v>
+        <v>0.7626144306135053</v>
       </c>
       <c r="D94">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E94">
         <v>5000</v>
       </c>
       <c r="F94">
-        <v>0.03494780729907127</v>
+        <v>0.03477016875603348</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3849,19 +3849,19 @@
         </is>
       </c>
       <c r="B95">
-        <v>14.70791124639109</v>
+        <v>15.63375581815578</v>
       </c>
       <c r="C95">
-        <v>0.5806906793105139</v>
+        <v>0.5424577888464703</v>
       </c>
       <c r="D95">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E95">
         <v>5000</v>
       </c>
       <c r="F95">
-        <v>0.08351637755010288</v>
+        <v>0.08851968038363911</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3886,19 +3886,19 @@
         </is>
       </c>
       <c r="B96">
-        <v>21.70875557462728</v>
+        <v>21.86867720689074</v>
       </c>
       <c r="C96">
-        <v>0.6280931344905551</v>
+        <v>0.624632734374808</v>
       </c>
       <c r="D96">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E96">
         <v>5000</v>
       </c>
       <c r="F96">
-        <v>0.03873572319932531</v>
+        <v>0.03898437893413208</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3923,19 +3923,19 @@
         </is>
       </c>
       <c r="B97">
-        <v>19.45628924388401</v>
+        <v>19.90966601597293</v>
       </c>
       <c r="C97">
-        <v>0.9073837108355408</v>
+        <v>0.9013605198604649</v>
       </c>
       <c r="D97">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E97">
         <v>5000</v>
       </c>
       <c r="F97">
-        <v>0.01805122121423542</v>
+        <v>0.01845104908250404</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3960,19 +3960,19 @@
         </is>
       </c>
       <c r="B98">
-        <v>19.98860807437589</v>
+        <v>20.33303829061299</v>
       </c>
       <c r="C98">
-        <v>0.9429509530338784</v>
+        <v>0.9395809982410758</v>
       </c>
       <c r="D98">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E98">
         <v>5000</v>
       </c>
       <c r="F98">
-        <v>0.01501377382768794</v>
+        <v>0.01525725477279841</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3997,19 +3997,19 @@
         </is>
       </c>
       <c r="B99">
-        <v>42.53061784250828</v>
+        <v>42.87433891158831</v>
       </c>
       <c r="C99">
-        <v>0.7861728546877362</v>
+        <v>0.7793899271519286</v>
       </c>
       <c r="D99">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E99">
         <v>5000</v>
       </c>
       <c r="F99">
-        <v>0.02646651574944804</v>
+        <v>0.02666049330389284</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4034,19 +4034,19 @@
         </is>
       </c>
       <c r="B100">
-        <v>48.78792303888461</v>
+        <v>48.13469981456862</v>
       </c>
       <c r="C100">
-        <v>0.7264199051578263</v>
+        <v>0.7302036793280426</v>
       </c>
       <c r="D100">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E100">
         <v>5000</v>
       </c>
       <c r="F100">
-        <v>0.02519791108807675</v>
+        <v>0.02484961581308007</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         </is>
       </c>
       <c r="B101">
-        <v>48.97986150834207</v>
+        <v>50.19934392228809</v>
       </c>
       <c r="C101">
-        <v>0.9236367756858402</v>
+        <v>0.9168474160122072</v>
       </c>
       <c r="D101">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E101">
         <v>5000</v>
       </c>
       <c r="F101">
-        <v>0.03389831702830367</v>
+        <v>0.03473073681941263</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4108,19 +4108,19 @@
         </is>
       </c>
       <c r="B102">
-        <v>14.51628715450107</v>
+        <v>14.93041017844698</v>
       </c>
       <c r="C102">
-        <v>0.5095911682584944</v>
+        <v>0.489768757093342</v>
       </c>
       <c r="D102">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E102">
         <v>5000</v>
       </c>
       <c r="F102">
-        <v>0.07833480999293221</v>
+        <v>0.08042091090085633</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4145,19 +4145,19 @@
         </is>
       </c>
       <c r="B103">
-        <v>24.03206844218367</v>
+        <v>24.58459857563569</v>
       </c>
       <c r="C103">
-        <v>0.8359723649541601</v>
+        <v>0.8349445056652982</v>
       </c>
       <c r="D103">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E103">
         <v>5000</v>
       </c>
       <c r="F103">
-        <v>0.03145836911998004</v>
+        <v>0.03211490042799103</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4182,19 +4182,19 @@
         </is>
       </c>
       <c r="B104">
-        <v>14.8908792350412</v>
+        <v>15.6009942487914</v>
       </c>
       <c r="C104">
-        <v>0.8079210668878968</v>
+        <v>0.7881828679871997</v>
       </c>
       <c r="D104">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E104">
         <v>5000</v>
       </c>
       <c r="F104">
-        <v>0.08293881253899209</v>
+        <v>0.08685232843374073</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="B105">
-        <v>21.51566597134377</v>
+        <v>22.6073761012845</v>
       </c>
       <c r="C105">
-        <v>0.9155181560815383</v>
+        <v>0.9063611580049967</v>
       </c>
       <c r="D105">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E105">
         <v>5000</v>
       </c>
       <c r="F105">
-        <v>0.01734983089834625</v>
+        <v>0.01821178070929022</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4256,19 +4256,19 @@
         </is>
       </c>
       <c r="B106">
-        <v>23.06464220090727</v>
+        <v>23.19149624354348</v>
       </c>
       <c r="C106">
-        <v>0.9182894644387942</v>
+        <v>0.9159226218099855</v>
       </c>
       <c r="D106">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E106">
         <v>5000</v>
       </c>
       <c r="F106">
-        <v>0.01886407218182473</v>
+        <v>0.01894957149839045</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4293,19 +4293,19 @@
         </is>
       </c>
       <c r="B107">
-        <v>23.41528956408289</v>
+        <v>23.79240646789727</v>
       </c>
       <c r="C107">
-        <v>0.9180918565863473</v>
+        <v>0.9109781659785325</v>
       </c>
       <c r="D107">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E107">
         <v>5000</v>
       </c>
       <c r="F107">
-        <v>0.01738328846628277</v>
+        <v>0.01766430557709238</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4330,19 +4330,19 @@
         </is>
       </c>
       <c r="B108">
-        <v>19.68256804611726</v>
+        <v>19.97730418804494</v>
       </c>
       <c r="C108">
-        <v>0.9295621547685526</v>
+        <v>0.9295148038930903</v>
       </c>
       <c r="D108">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E108">
         <v>5000</v>
       </c>
       <c r="F108">
-        <v>0.01804062718043819</v>
+        <v>0.01828061900298154</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4367,19 +4367,19 @@
         </is>
       </c>
       <c r="B109">
-        <v>29.69861979644852</v>
+        <v>30.50297600540286</v>
       </c>
       <c r="C109">
-        <v>0.7196033110911084</v>
+        <v>0.704348600145192</v>
       </c>
       <c r="D109">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E109">
         <v>5000</v>
       </c>
       <c r="F109">
-        <v>0.08457563459446568</v>
+        <v>0.08673832039451049</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4404,19 +4404,19 @@
         </is>
       </c>
       <c r="B110">
-        <v>25.75303452671607</v>
+        <v>25.64529818587017</v>
       </c>
       <c r="C110">
-        <v>0.7266104991890638</v>
+        <v>0.7345289777458032</v>
       </c>
       <c r="D110">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E110">
         <v>5000</v>
       </c>
       <c r="F110">
-        <v>0.05084101363186931</v>
+        <v>0.05051999800221325</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="B111">
-        <v>13.12273858684518</v>
+        <v>13.63679635671438</v>
       </c>
       <c r="C111">
-        <v>0.5718360291588401</v>
+        <v>0.5413666263561389</v>
       </c>
       <c r="D111">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E111">
         <v>5000</v>
       </c>
       <c r="F111">
-        <v>0.08914740249945319</v>
+        <v>0.0927168639972422</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="B112">
-        <v>19.7631167399577</v>
+        <v>19.17385942273984</v>
       </c>
       <c r="C112">
-        <v>0.9255948167830127</v>
+        <v>0.9301368806053913</v>
       </c>
       <c r="D112">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E112">
         <v>5000</v>
       </c>
       <c r="F112">
-        <v>0.01795566107327125</v>
+        <v>0.01740335782047063</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="B113">
-        <v>82.17481764028624</v>
+        <v>83.06338689347334</v>
       </c>
       <c r="C113">
-        <v>0.6082294308599316</v>
+        <v>0.5962213032946173</v>
       </c>
       <c r="D113">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E113">
         <v>5000</v>
       </c>
       <c r="F113">
-        <v>0.03420849626960459</v>
+        <v>0.03455119945098861</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4552,19 +4552,19 @@
         </is>
       </c>
       <c r="B114">
-        <v>35.63491498853003</v>
+        <v>35.3516266595318</v>
       </c>
       <c r="C114">
-        <v>0.934147614731815</v>
+        <v>0.9361904658546274</v>
       </c>
       <c r="D114">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E114">
         <v>5000</v>
       </c>
       <c r="F114">
-        <v>0.03465247061882339</v>
+        <v>0.03433485709152802</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4589,19 +4589,19 @@
         </is>
       </c>
       <c r="B115">
-        <v>20.96649374268461</v>
+        <v>21.34139615752571</v>
       </c>
       <c r="C115">
-        <v>0.9285992778347506</v>
+        <v>0.9254961468140795</v>
       </c>
       <c r="D115">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E115">
         <v>5000</v>
       </c>
       <c r="F115">
-        <v>0.01766403525882235</v>
+        <v>0.01798230212127208</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4626,19 +4626,19 @@
         </is>
       </c>
       <c r="B116">
-        <v>24.19802068284872</v>
+        <v>24.79212198037272</v>
       </c>
       <c r="C116">
-        <v>0.6519924339343163</v>
+        <v>0.6505813846828479</v>
       </c>
       <c r="D116">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E116">
         <v>5000</v>
       </c>
       <c r="F116">
-        <v>0.05377014985678955</v>
+        <v>0.05494220809408013</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4663,19 +4663,19 @@
         </is>
       </c>
       <c r="B117">
-        <v>17.3872445041892</v>
+        <v>17.29954012214074</v>
       </c>
       <c r="C117">
-        <v>0.9383762455105361</v>
+        <v>0.9404256685233807</v>
       </c>
       <c r="D117">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E117">
         <v>5000</v>
       </c>
       <c r="F117">
-        <v>0.01482544728254233</v>
+        <v>0.01473220743908886</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="B118">
-        <v>10.21886668722291</v>
+        <v>10.3886875896616</v>
       </c>
       <c r="C118">
-        <v>0.5264953358402935</v>
+        <v>0.5307933765726397</v>
       </c>
       <c r="D118">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E118">
         <v>5000</v>
       </c>
       <c r="F118">
-        <v>0.09180479966668634</v>
+        <v>0.09275613919340718</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4737,19 +4737,19 @@
         </is>
       </c>
       <c r="B119">
-        <v>17.44458988622317</v>
+        <v>17.90106762432711</v>
       </c>
       <c r="C119">
-        <v>0.4923497259503128</v>
+        <v>0.4632913559344619</v>
       </c>
       <c r="D119">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E119">
         <v>5000</v>
       </c>
       <c r="F119">
-        <v>0.0659227684394094</v>
+        <v>0.06770449177128257</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4774,19 +4774,19 @@
         </is>
       </c>
       <c r="B120">
-        <v>25.87028283110712</v>
+        <v>27.05250554362715</v>
       </c>
       <c r="C120">
-        <v>0.86436633027183</v>
+        <v>0.8489961236296948</v>
       </c>
       <c r="D120">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E120">
         <v>5000</v>
       </c>
       <c r="F120">
-        <v>0.0370612898945296</v>
+        <v>0.03872831922296734</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4811,19 +4811,19 @@
         </is>
       </c>
       <c r="B121">
-        <v>13.24553357542341</v>
+        <v>13.77598273246653</v>
       </c>
       <c r="C121">
-        <v>0.4752201168365479</v>
+        <v>0.442431201844157</v>
       </c>
       <c r="D121">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E121">
         <v>5000</v>
       </c>
       <c r="F121">
-        <v>0.08211187773991224</v>
+        <v>0.08533190493351415</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4848,19 +4848,19 @@
         </is>
       </c>
       <c r="B122">
-        <v>20.6080390124282</v>
+        <v>19.00074919863172</v>
       </c>
       <c r="C122">
-        <v>0.9514560113556498</v>
+        <v>0.9547530078762125</v>
       </c>
       <c r="D122">
-        <v>1211.402777777778</v>
+        <v>1213.6</v>
       </c>
       <c r="E122">
         <v>10000</v>
       </c>
       <c r="F122">
-        <v>0.01701171517059917</v>
+        <v>0.01565651713796285</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4885,19 +4885,19 @@
         </is>
       </c>
       <c r="B123">
-        <v>22.3758382952796</v>
+        <v>21.09191543642686</v>
       </c>
       <c r="C123">
-        <v>0.8509499441786676</v>
+        <v>0.8745282087936072</v>
       </c>
       <c r="D123">
-        <v>644.4583333333334</v>
+        <v>647.6799999999999</v>
       </c>
       <c r="E123">
         <v>10000</v>
       </c>
       <c r="F123">
-        <v>0.03472038010517297</v>
+        <v>0.03256533386306024</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4922,19 +4922,19 @@
         </is>
       </c>
       <c r="B124">
-        <v>19.93655677924836</v>
+        <v>19.11874366893998</v>
       </c>
       <c r="C124">
-        <v>0.8037997626605078</v>
+        <v>0.8224889272813759</v>
       </c>
       <c r="D124">
-        <v>629.8243243243244</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="E124">
         <v>10000</v>
       </c>
       <c r="F124">
-        <v>0.03165415499097515</v>
+        <v>0.03031449176910633</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="B125">
-        <v>13.93792031993645</v>
+        <v>13.15444472601383</v>
       </c>
       <c r="C125">
-        <v>0.6261677993356689</v>
+        <v>0.6803866431987857</v>
       </c>
       <c r="D125">
-        <v>176.1081081081081</v>
+        <v>176.6133333333333</v>
       </c>
       <c r="E125">
         <v>10000</v>
       </c>
       <c r="F125">
-        <v>0.0791441147694366</v>
+        <v>0.07448160610380772</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4996,19 +4996,19 @@
         </is>
       </c>
       <c r="B126">
-        <v>19.73577554505489</v>
+        <v>18.52969359031975</v>
       </c>
       <c r="C126">
-        <v>0.6941380682853431</v>
+        <v>0.7397730613516712</v>
       </c>
       <c r="D126">
-        <v>560.4324324324324</v>
+        <v>560.96</v>
       </c>
       <c r="E126">
         <v>10000</v>
       </c>
       <c r="F126">
-        <v>0.03521526307711376</v>
+        <v>0.03303211207629732</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5033,19 +5033,19 @@
         </is>
       </c>
       <c r="B127">
-        <v>17.69313332939507</v>
+        <v>17.01440381247761</v>
       </c>
       <c r="C127">
-        <v>0.9241061487464577</v>
+        <v>0.9288929230518648</v>
       </c>
       <c r="D127">
-        <v>1077.837837837838</v>
+        <v>1079.053333333333</v>
       </c>
       <c r="E127">
         <v>10000</v>
       </c>
       <c r="F127">
-        <v>0.01641539451323012</v>
+        <v>0.01576789884881588</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5070,19 +5070,19 @@
         </is>
       </c>
       <c r="B128">
-        <v>19.04289682021802</v>
+        <v>18.01927145730358</v>
       </c>
       <c r="C128">
-        <v>0.9472173449357132</v>
+        <v>0.9514105039592577</v>
       </c>
       <c r="D128">
-        <v>1331.351351351351</v>
+        <v>1332.68</v>
       </c>
       <c r="E128">
         <v>10000</v>
       </c>
       <c r="F128">
-        <v>0.01430343447722425</v>
+        <v>0.01352107892164929</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5107,19 +5107,19 @@
         </is>
       </c>
       <c r="B129">
-        <v>42.56427582707325</v>
+        <v>40.33256608680623</v>
       </c>
       <c r="C129">
-        <v>0.7825952983593668</v>
+        <v>0.8090731678303972</v>
       </c>
       <c r="D129">
-        <v>1606.959459459459</v>
+        <v>1608.16</v>
       </c>
       <c r="E129">
         <v>10000</v>
       </c>
       <c r="F129">
-        <v>0.02648746088553522</v>
+        <v>0.02507994607924972</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5144,19 +5144,19 @@
         </is>
       </c>
       <c r="B130">
-        <v>47.77797168704121</v>
+        <v>46.61915396983377</v>
       </c>
       <c r="C130">
-        <v>0.7392478539354018</v>
+        <v>0.7512353144969823</v>
       </c>
       <c r="D130">
-        <v>1936.189189189189</v>
+        <v>1937.04</v>
       </c>
       <c r="E130">
         <v>10000</v>
       </c>
       <c r="F130">
-        <v>0.02467629297478363</v>
+        <v>0.02406721284528651</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5181,19 +5181,19 @@
         </is>
       </c>
       <c r="B131">
-        <v>47.77430373358026</v>
+        <v>45.3431739436083</v>
       </c>
       <c r="C131">
-        <v>0.9267504114333102</v>
+        <v>0.9340142353330475</v>
       </c>
       <c r="D131">
-        <v>1444.905405405405</v>
+        <v>1445.386666666667</v>
       </c>
       <c r="E131">
         <v>10000</v>
       </c>
       <c r="F131">
-        <v>0.03306396637098603</v>
+        <v>0.03137096459328643</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5218,19 +5218,19 @@
         </is>
       </c>
       <c r="B132">
-        <v>14.29943609384425</v>
+        <v>13.31563143094957</v>
       </c>
       <c r="C132">
-        <v>0.5245923551882982</v>
+        <v>0.5888414716957031</v>
       </c>
       <c r="D132">
-        <v>185.3108108108108</v>
+        <v>185.6533333333333</v>
       </c>
       <c r="E132">
         <v>10000</v>
       </c>
       <c r="F132">
-        <v>0.07716460810504443</v>
+        <v>0.07172309374613746</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5255,19 +5255,19 @@
         </is>
       </c>
       <c r="B133">
-        <v>22.48720172934966</v>
+        <v>21.34795079180643</v>
       </c>
       <c r="C133">
-        <v>0.8566134735789308</v>
+        <v>0.8768364374383216</v>
       </c>
       <c r="D133">
-        <v>763.9324324324324</v>
+        <v>765.52</v>
       </c>
       <c r="E133">
         <v>10000</v>
       </c>
       <c r="F133">
-        <v>0.02943611342399523</v>
+        <v>0.02788686225285614</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5292,19 +5292,19 @@
         </is>
       </c>
       <c r="B134">
-        <v>14.10936972275139</v>
+        <v>13.05272452653067</v>
       </c>
       <c r="C134">
-        <v>0.8281683558379829</v>
+        <v>0.852822414229893</v>
       </c>
       <c r="D134">
-        <v>179.5405405405405</v>
+        <v>179.6266666666667</v>
       </c>
       <c r="E134">
         <v>10000</v>
       </c>
       <c r="F134">
-        <v>0.07858598219807339</v>
+        <v>0.07266585061533552</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5329,19 +5329,19 @@
         </is>
       </c>
       <c r="B135">
-        <v>20.04237451665426</v>
+        <v>17.79896703425821</v>
       </c>
       <c r="C135">
-        <v>0.9284802130570101</v>
+        <v>0.9436206844921615</v>
       </c>
       <c r="D135">
-        <v>1240.108108108108</v>
+        <v>1241.36</v>
       </c>
       <c r="E135">
         <v>10000</v>
       </c>
       <c r="F135">
-        <v>0.01616179620600226</v>
+        <v>0.01433827981750516</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5366,19 +5366,19 @@
         </is>
       </c>
       <c r="B136">
-        <v>21.50103432478701</v>
+        <v>19.60083809979842</v>
       </c>
       <c r="C136">
-        <v>0.929857030213429</v>
+        <v>0.941705148144685</v>
       </c>
       <c r="D136">
-        <v>1222.675675675676</v>
+        <v>1223.853333333333</v>
       </c>
       <c r="E136">
         <v>10000</v>
       </c>
       <c r="F136">
-        <v>0.01758523110628262</v>
+        <v>0.01601567570716406</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5403,19 +5403,19 @@
         </is>
       </c>
       <c r="B137">
-        <v>21.98353026581539</v>
+        <v>19.8475482932082</v>
       </c>
       <c r="C137">
-        <v>0.9275522559375604</v>
+        <v>0.9399467833407141</v>
       </c>
       <c r="D137">
-        <v>1347</v>
+        <v>1346.92</v>
       </c>
       <c r="E137">
         <v>10000</v>
       </c>
       <c r="F137">
-        <v>0.01632036396868254</v>
+        <v>0.0147355064095924</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5440,19 +5440,19 @@
         </is>
       </c>
       <c r="B138">
-        <v>18.72658922260702</v>
+        <v>17.23476796739308</v>
       </c>
       <c r="C138">
-        <v>0.935286560250408</v>
+        <v>0.9470662172923994</v>
       </c>
       <c r="D138">
-        <v>1091.013513513514</v>
+        <v>1092.813333333333</v>
       </c>
       <c r="E138">
         <v>10000</v>
       </c>
       <c r="F138">
-        <v>0.01716439713225886</v>
+        <v>0.01577100813258112</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5477,19 +5477,19 @@
         </is>
       </c>
       <c r="B139">
-        <v>28.49777808899296</v>
+        <v>26.82932809847197</v>
       </c>
       <c r="C139">
-        <v>0.7399034613426383</v>
+        <v>0.7694697747370124</v>
       </c>
       <c r="D139">
-        <v>351.1486486486486</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="E139">
         <v>10000</v>
       </c>
       <c r="F139">
-        <v>0.08115588141564284</v>
+        <v>0.07629192824210038</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5514,19 +5514,19 @@
         </is>
       </c>
       <c r="B140">
-        <v>23.87869021187534</v>
+        <v>22.074975862313</v>
       </c>
       <c r="C140">
-        <v>0.7646643197038533</v>
+        <v>0.8045955587838751</v>
       </c>
       <c r="D140">
-        <v>506.5405405405405</v>
+        <v>507.6266666666667</v>
       </c>
       <c r="E140">
         <v>10000</v>
       </c>
       <c r="F140">
-        <v>0.04714072872902507</v>
+        <v>0.04348663557663046</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5551,19 +5551,19 @@
         </is>
       </c>
       <c r="B141">
-        <v>12.68251183271602</v>
+        <v>12.06346621224281</v>
       </c>
       <c r="C141">
-        <v>0.6033846662783214</v>
+        <v>0.6451298816145755</v>
       </c>
       <c r="D141">
-        <v>147.2027027027027</v>
+        <v>147.08</v>
       </c>
       <c r="E141">
         <v>10000</v>
       </c>
       <c r="F141">
-        <v>0.08615678652538193</v>
+        <v>0.08201975939789781</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5588,19 +5588,19 @@
         </is>
       </c>
       <c r="B142">
-        <v>17.83085441099693</v>
+        <v>16.42544228799067</v>
       </c>
       <c r="C142">
-        <v>0.9408559324930762</v>
+        <v>0.9498896460668695</v>
       </c>
       <c r="D142">
-        <v>1100.662162162162</v>
+        <v>1101.733333333333</v>
       </c>
       <c r="E142">
         <v>10000</v>
       </c>
       <c r="F142">
-        <v>0.01620011573394115</v>
+        <v>0.01490872772115817</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5625,19 +5625,19 @@
         </is>
       </c>
       <c r="B143">
-        <v>80.73235436703081</v>
+        <v>85.187014234039</v>
       </c>
       <c r="C143">
-        <v>0.6113486914799645</v>
+        <v>0.5868089614065916</v>
       </c>
       <c r="D143">
-        <v>2402.175675675676</v>
+        <v>2404.066666666667</v>
       </c>
       <c r="E143">
         <v>10000</v>
       </c>
       <c r="F143">
-        <v>0.03360801426162251</v>
+        <v>0.03543454739221278</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5662,19 +5662,19 @@
         </is>
       </c>
       <c r="B144">
-        <v>31.73368188746328</v>
+        <v>29.35225882835937</v>
       </c>
       <c r="C144">
-        <v>0.9486275651005184</v>
+        <v>0.956437997624304</v>
       </c>
       <c r="D144">
-        <v>1028.351351351351</v>
+        <v>1029.613333333333</v>
       </c>
       <c r="E144">
         <v>10000</v>
       </c>
       <c r="F144">
-        <v>0.0308587933936803</v>
+        <v>0.02850804071595749</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5699,19 +5699,19 @@
         </is>
       </c>
       <c r="B145">
-        <v>18.76076842828314</v>
+        <v>17.93832447185853</v>
       </c>
       <c r="C145">
-        <v>0.9456302332269145</v>
+        <v>0.9489861252349711</v>
       </c>
       <c r="D145">
-        <v>1186.959459459459</v>
+        <v>1186.8</v>
       </c>
       <c r="E145">
         <v>10000</v>
       </c>
       <c r="F145">
-        <v>0.01580573647968296</v>
+        <v>0.01511486726648005</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5736,19 +5736,19 @@
         </is>
       </c>
       <c r="B146">
-        <v>23.32088505493221</v>
+        <v>22.56584104764873</v>
       </c>
       <c r="C146">
-        <v>0.6741081335945378</v>
+        <v>0.7075277109329731</v>
       </c>
       <c r="D146">
-        <v>450.027027027027</v>
+        <v>451.24</v>
       </c>
       <c r="E146">
         <v>10000</v>
       </c>
       <c r="F146">
-        <v>0.05182107663398545</v>
+        <v>0.05000851220558623</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5773,19 +5773,19 @@
         </is>
       </c>
       <c r="B147">
-        <v>16.14656590689415</v>
+        <v>14.84361898043181</v>
       </c>
       <c r="C147">
-        <v>0.9477214215086833</v>
+        <v>0.956996408199126</v>
       </c>
       <c r="D147">
-        <v>1172.797297297297</v>
+        <v>1174.266666666667</v>
       </c>
       <c r="E147">
         <v>10000</v>
       </c>
       <c r="F147">
-        <v>0.01376756745952927</v>
+        <v>0.01264075648384678</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="B148">
-        <v>9.915593484017061</v>
+        <v>9.278493291347139</v>
       </c>
       <c r="C148">
-        <v>0.5502982375288072</v>
+        <v>0.6279939342994494</v>
       </c>
       <c r="D148">
-        <v>111.3108108108108</v>
+        <v>112</v>
       </c>
       <c r="E148">
         <v>10000</v>
       </c>
       <c r="F148">
-        <v>0.08908023768571841</v>
+        <v>0.08284369010131375</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5847,19 +5847,19 @@
         </is>
       </c>
       <c r="B149">
-        <v>17.33862773010066</v>
+        <v>16.66164536727196</v>
       </c>
       <c r="C149">
-        <v>0.4951523860447896</v>
+        <v>0.5344099964236286</v>
       </c>
       <c r="D149">
-        <v>264.6216216216216</v>
+        <v>264.4</v>
       </c>
       <c r="E149">
         <v>10000</v>
       </c>
       <c r="F149">
-        <v>0.06552233949685675</v>
+        <v>0.06301681303809363</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5884,19 +5884,19 @@
         </is>
       </c>
       <c r="B150">
-        <v>23.92599936317805</v>
+        <v>23.11078257039194</v>
       </c>
       <c r="C150">
-        <v>0.8857918338886452</v>
+        <v>0.8918189588328582</v>
       </c>
       <c r="D150">
-        <v>698.0405405405405</v>
+        <v>698.52</v>
       </c>
       <c r="E150">
         <v>10000</v>
       </c>
       <c r="F150">
-        <v>0.03427594526909642</v>
+        <v>0.03308535556661505</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5921,19 +5921,19 @@
         </is>
       </c>
       <c r="B151">
-        <v>12.58232325562051</v>
+        <v>11.81452399540128</v>
       </c>
       <c r="C151">
-        <v>0.525222216250274</v>
+        <v>0.5780799655377387</v>
       </c>
       <c r="D151">
-        <v>161.3108108108108</v>
+        <v>161.44</v>
       </c>
       <c r="E151">
         <v>10000</v>
       </c>
       <c r="F151">
-        <v>0.07800049601373191</v>
+        <v>0.07318213574951236</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
